--- a/tests/fixtures/01_simple_invoice/pattern.xlsx
+++ b/tests/fixtures/01_simple_invoice/pattern.xlsx
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>def:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
